--- a/ozone/multistate/test_ozone_VTZP_MS_1_90_10_split_energies.xlsx
+++ b/ozone/multistate/test_ozone_VTZP_MS_1_90_10_split_energies.xlsx
@@ -485,7 +485,7 @@
         <v>-0.5613927663232834</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5621004104614258</v>
+        <v>-0.5620771646499634</v>
       </c>
       <c r="F2" t="n">
         <v>-225.26426644</v>
@@ -494,7 +494,7 @@
         <v>-224.70286911</v>
       </c>
       <c r="H2" t="n">
-        <v>-225.2649695204614</v>
+        <v>-225.26494627465</v>
       </c>
     </row>
     <row r="3">
@@ -517,7 +517,7 @@
         <v>-0.5607089802995817</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.548771858215332</v>
+        <v>-0.5476018190383911</v>
       </c>
       <c r="F3" t="n">
         <v>-225.29099234</v>
@@ -526,7 +526,7 @@
         <v>-224.73028554</v>
       </c>
       <c r="H3" t="n">
-        <v>-225.2790573982153</v>
+        <v>-225.2778873590384</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +549,7 @@
         <v>-0.5775355144535526</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.58460932970047</v>
+        <v>-0.5834774971008301</v>
       </c>
       <c r="F4" t="n">
         <v>-225.15714931</v>
@@ -558,7 +558,7 @@
         <v>-224.57961155</v>
       </c>
       <c r="H4" t="n">
-        <v>-225.1642208797005</v>
+        <v>-225.1630890471008</v>
       </c>
     </row>
     <row r="5">
@@ -581,7 +581,7 @@
         <v>-0.5606721642141721</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5597442388534546</v>
+        <v>-0.5592919588088989</v>
       </c>
       <c r="F5" t="n">
         <v>-225.28874778</v>
@@ -590,7 +590,7 @@
         <v>-224.72807417</v>
       </c>
       <c r="H5" t="n">
-        <v>-225.2878184088535</v>
+        <v>-225.2873661288089</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         <v>-0.562385397589843</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5626612901687622</v>
+        <v>-0.5631162524223328</v>
       </c>
       <c r="F6" t="n">
         <v>-225.23626113</v>
@@ -622,7 +622,7 @@
         <v>-224.67387393</v>
       </c>
       <c r="H6" t="n">
-        <v>-225.2365352201688</v>
+        <v>-225.2369901824223</v>
       </c>
     </row>
     <row r="7">
@@ -645,7 +645,7 @@
         <v>-0.56968356548406</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5719484686851501</v>
+        <v>-0.5718016624450684</v>
       </c>
       <c r="F7" t="n">
         <v>-225.19788659</v>
@@ -654,7 +654,7 @@
         <v>-224.62820748</v>
       </c>
       <c r="H7" t="n">
-        <v>-225.2001559486851</v>
+        <v>-225.2000091424451</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         <v>-0.5604939663242526</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5593021512031555</v>
+        <v>-0.5595843195915222</v>
       </c>
       <c r="F8" t="n">
         <v>-225.29774517</v>
@@ -686,7 +686,7 @@
         <v>-224.73725447</v>
       </c>
       <c r="H8" t="n">
-        <v>-225.2965566212032</v>
+        <v>-225.2968387895915</v>
       </c>
     </row>
     <row r="9">
@@ -709,7 +709,7 @@
         <v>-0.5605759870745084</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5616203546524048</v>
+        <v>-0.5605621337890625</v>
       </c>
       <c r="F9" t="n">
         <v>-225.29532525</v>
@@ -718,7 +718,7 @@
         <v>-224.73475163</v>
       </c>
       <c r="H9" t="n">
-        <v>-225.2963719846524</v>
+        <v>-225.2953137637891</v>
       </c>
     </row>
     <row r="10">
@@ -741,7 +741,7 @@
         <v>-0.5709448222752113</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5704377889633179</v>
+        <v>-0.5707313418388367</v>
       </c>
       <c r="F10" t="n">
         <v>-225.18583249</v>
@@ -750,7 +750,7 @@
         <v>-224.61488873</v>
       </c>
       <c r="H10" t="n">
-        <v>-225.1853265189633</v>
+        <v>-225.1856200718388</v>
       </c>
     </row>
     <row r="11">
@@ -773,7 +773,7 @@
         <v>-0.5604521369994631</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.559111475944519</v>
+        <v>-0.5598728656768799</v>
       </c>
       <c r="F11" t="n">
         <v>-225.29831097</v>
@@ -782,7 +782,7 @@
         <v>-224.73786008</v>
       </c>
       <c r="H11" t="n">
-        <v>-225.2969715559445</v>
+        <v>-225.2977329456769</v>
       </c>
     </row>
     <row r="12">
@@ -805,7 +805,7 @@
         <v>-0.563308038496113</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5594433546066284</v>
+        <v>-0.5593873262405396</v>
       </c>
       <c r="F12" t="n">
         <v>-225.21499993</v>
@@ -814,7 +814,7 @@
         <v>-224.65169138</v>
       </c>
       <c r="H12" t="n">
-        <v>-225.2111347346066</v>
+        <v>-225.2110787062405</v>
       </c>
     </row>
     <row r="13">
@@ -837,7 +837,7 @@
         <v>-0.56265161045073</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5557897090911865</v>
+        <v>-0.5559508800506592</v>
       </c>
       <c r="F13" t="n">
         <v>-225.22964682</v>
@@ -846,7 +846,7 @@
         <v>-224.66699324</v>
       </c>
       <c r="H13" t="n">
-        <v>-225.2227829490912</v>
+        <v>-225.2229441200507</v>
       </c>
     </row>
     <row r="14">
@@ -869,7 +869,7 @@
         <v>-0.5604582456641501</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.561188280582428</v>
+        <v>-0.5604954957962036</v>
       </c>
       <c r="F14" t="n">
         <v>-225.29762607</v>
@@ -878,7 +878,7 @@
         <v>-224.7371667</v>
       </c>
       <c r="H14" t="n">
-        <v>-225.2983549805824</v>
+        <v>-225.2976621957962</v>
       </c>
     </row>
     <row r="15">
@@ -901,7 +901,7 @@
         <v>-0.5615508642955024</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.560923159122467</v>
+        <v>-0.5611728429794312</v>
       </c>
       <c r="F15" t="n">
         <v>-225.25959092</v>
@@ -910,7 +910,7 @@
         <v>-224.69804114</v>
       </c>
       <c r="H15" t="n">
-        <v>-225.2589642991225</v>
+        <v>-225.2592139829794</v>
       </c>
     </row>
     <row r="16">
@@ -933,7 +933,7 @@
         <v>-0.572963651777042</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5710186958312988</v>
+        <v>-0.5708032250404358</v>
       </c>
       <c r="F16" t="n">
         <v>-225.17233859</v>
@@ -942,7 +942,7 @@
         <v>-224.59937454</v>
       </c>
       <c r="H16" t="n">
-        <v>-225.1703932358313</v>
+        <v>-225.1701777650404</v>
       </c>
     </row>
     <row r="17">
@@ -965,7 +965,7 @@
         <v>-0.5628723669011582</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.564013659954071</v>
+        <v>-0.5642893314361572</v>
       </c>
       <c r="F17" t="n">
         <v>-225.22455837</v>
@@ -974,7 +974,7 @@
         <v>-224.66168882</v>
       </c>
       <c r="H17" t="n">
-        <v>-225.2257024799541</v>
+        <v>-225.2259781514362</v>
       </c>
     </row>
     <row r="18">
@@ -997,7 +997,7 @@
         <v>-0.5685840137018696</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5722106099128723</v>
+        <v>-0.5721733570098877</v>
       </c>
       <c r="F18" t="n">
         <v>-225.21102459</v>
@@ -1006,7 +1006,7 @@
         <v>-224.6424398</v>
       </c>
       <c r="H18" t="n">
-        <v>-225.2146504099129</v>
+        <v>-225.2146131570099</v>
       </c>
     </row>
     <row r="19">
@@ -1029,7 +1029,7 @@
         <v>-0.5711489853097031</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5694632530212402</v>
+        <v>-0.5701033473014832</v>
       </c>
       <c r="F19" t="n">
         <v>-225.18415873</v>
@@ -1038,7 +1038,7 @@
         <v>-224.61300884</v>
       </c>
       <c r="H19" t="n">
-        <v>-225.1824720930212</v>
+        <v>-225.1831121873015</v>
       </c>
     </row>
     <row r="20">
@@ -1061,7 +1061,7 @@
         <v>-0.5606373091302363</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5618264079093933</v>
+        <v>-0.5615782737731934</v>
       </c>
       <c r="F20" t="n">
         <v>-225.29324447</v>
@@ -1070,7 +1070,7 @@
         <v>-224.73260567</v>
       </c>
       <c r="H20" t="n">
-        <v>-225.2944320779094</v>
+        <v>-225.2941839437732</v>
       </c>
     </row>
     <row r="21">
@@ -1093,7 +1093,7 @@
         <v>-0.5797162441902822</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5769902467727661</v>
+        <v>-0.5783811211585999</v>
       </c>
       <c r="F21" t="n">
         <v>-225.15401052</v>
@@ -1102,7 +1102,7 @@
         <v>-224.57429448</v>
       </c>
       <c r="H21" t="n">
-        <v>-225.1512847267728</v>
+        <v>-225.1526756011586</v>
       </c>
     </row>
     <row r="22">
@@ -1125,7 +1125,7 @@
         <v>-0.5606561418753</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5612367391586304</v>
+        <v>-0.5607624053955078</v>
       </c>
       <c r="F22" t="n">
         <v>-225.28949128</v>
@@ -1134,7 +1134,7 @@
         <v>-224.72883736</v>
       </c>
       <c r="H22" t="n">
-        <v>-225.2900740991586</v>
+        <v>-225.2895997653955</v>
       </c>
     </row>
     <row r="23">
@@ -1157,7 +1157,7 @@
         <v>-0.560594523113199</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5607344508171082</v>
+        <v>-0.5609273910522461</v>
       </c>
       <c r="F23" t="n">
         <v>-225.29188001</v>
@@ -1166,7 +1166,7 @@
         <v>-224.73128797</v>
       </c>
       <c r="H23" t="n">
-        <v>-225.2920224208171</v>
+        <v>-225.2922153610523</v>
       </c>
     </row>
     <row r="24">
@@ -1189,7 +1189,7 @@
         <v>-0.5725558735505254</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5734964609146118</v>
+        <v>-0.5730971097946167</v>
       </c>
       <c r="F24" t="n">
         <v>-225.17457306</v>
@@ -1198,7 +1198,7 @@
         <v>-224.60201355</v>
       </c>
       <c r="H24" t="n">
-        <v>-225.1755100109146</v>
+        <v>-225.1751106597946</v>
       </c>
     </row>
     <row r="25">
@@ -1221,7 +1221,7 @@
         <v>-0.5786019433972763</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5753395557403564</v>
+        <v>-0.5749609470367432</v>
       </c>
       <c r="F25" t="n">
         <v>-225.15535756</v>
@@ -1230,7 +1230,7 @@
         <v>-224.57675806</v>
       </c>
       <c r="H25" t="n">
-        <v>-225.1520976157404</v>
+        <v>-225.1517190070367</v>
       </c>
     </row>
     <row r="26">
@@ -1253,7 +1253,7 @@
         <v>-0.5617677988057698</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5631880760192871</v>
+        <v>-0.5633457899093628</v>
       </c>
       <c r="F26" t="n">
         <v>-225.25323833</v>
@@ -1262,7 +1262,7 @@
         <v>-224.69147383</v>
       </c>
       <c r="H26" t="n">
-        <v>-225.2546619060193</v>
+        <v>-225.2548196199094</v>
       </c>
     </row>
     <row r="27">
@@ -1285,7 +1285,7 @@
         <v>-0.5604508188336887</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5600509643554688</v>
+        <v>-0.561068058013916</v>
       </c>
       <c r="F27" t="n">
         <v>-225.29825541</v>
@@ -1294,7 +1294,7 @@
         <v>-224.7378043</v>
       </c>
       <c r="H27" t="n">
-        <v>-225.2978552643555</v>
+        <v>-225.2988723580139</v>
       </c>
     </row>
     <row r="28">
@@ -1317,7 +1317,7 @@
         <v>-0.5606493535420561</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5630858540534973</v>
+        <v>-0.5629579424858093</v>
       </c>
       <c r="F28" t="n">
         <v>-225.29290004</v>
@@ -1326,7 +1326,7 @@
         <v>-224.73225066</v>
       </c>
       <c r="H28" t="n">
-        <v>-225.2953365140535</v>
+        <v>-225.2952086024858</v>
       </c>
     </row>
     <row r="29">
@@ -1349,7 +1349,7 @@
         <v>-0.5693676746070553</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5698124170303345</v>
+        <v>-0.5696815252304077</v>
       </c>
       <c r="F29" t="n">
         <v>-225.20138958</v>
@@ -1358,7 +1358,7 @@
         <v>-224.63202431</v>
       </c>
       <c r="H29" t="n">
-        <v>-225.2018367270303</v>
+        <v>-225.2017058352304</v>
       </c>
     </row>
     <row r="30">
@@ -1381,7 +1381,7 @@
         <v>-0.5604872948099939</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.562127947807312</v>
+        <v>-0.562814474105835</v>
       </c>
       <c r="F30" t="n">
         <v>-225.2962232</v>
@@ -1390,7 +1390,7 @@
         <v>-224.73573594</v>
       </c>
       <c r="H30" t="n">
-        <v>-225.2978638878073</v>
+        <v>-225.2985504141058</v>
       </c>
     </row>
     <row r="31">
@@ -1413,7 +1413,7 @@
         <v>-0.5610423406037672</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5641544461250305</v>
+        <v>-0.5638452172279358</v>
       </c>
       <c r="F31" t="n">
         <v>-225.27568979</v>
@@ -1422,7 +1422,7 @@
         <v>-224.71464609</v>
       </c>
       <c r="H31" t="n">
-        <v>-225.278800536125</v>
+        <v>-225.2784913072279</v>
       </c>
     </row>
     <row r="32">
@@ -1445,7 +1445,7 @@
         <v>-0.5619188996383899</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5609524250030518</v>
+        <v>-0.5605001449584961</v>
       </c>
       <c r="F32" t="n">
         <v>-225.24880252</v>
@@ -1454,7 +1454,7 @@
         <v>-224.68688256</v>
       </c>
       <c r="H32" t="n">
-        <v>-225.247834985003</v>
+        <v>-225.2473827049585</v>
       </c>
     </row>
   </sheetData>
